--- a/data/dataframe_processed.xlsx
+++ b/data/dataframe_processed.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G315"/>
+  <dimension ref="A1:F315"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -456,11 +456,6 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>BV Actuated</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
           <t>Severity</t>
         </is>
       </c>
@@ -487,10 +482,7 @@
           <t>Heater (ISC)</t>
         </is>
       </c>
-      <c r="F2" t="b">
-        <v>1</v>
-      </c>
-      <c r="G2" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -518,10 +510,7 @@
           <t>Heater (ISC)</t>
         </is>
       </c>
-      <c r="F3" t="b">
-        <v>1</v>
-      </c>
-      <c r="G3" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -549,10 +538,7 @@
           <t>Heater (ISC)</t>
         </is>
       </c>
-      <c r="F4" t="b">
-        <v>0</v>
-      </c>
-      <c r="G4" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -580,10 +566,7 @@
           <t>Heater (ISC)</t>
         </is>
       </c>
-      <c r="F5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G5" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -611,10 +594,7 @@
           <t>Heater (ISC)</t>
         </is>
       </c>
-      <c r="F6" t="b">
-        <v>1</v>
-      </c>
-      <c r="G6" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>High</t>
         </is>
@@ -642,10 +622,7 @@
           <t>Heater (ISC)</t>
         </is>
       </c>
-      <c r="F7" t="b">
-        <v>0</v>
-      </c>
-      <c r="G7" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -673,10 +650,7 @@
           <t>Heater (ISC)</t>
         </is>
       </c>
-      <c r="F8" t="b">
-        <v>1</v>
-      </c>
-      <c r="G8" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -704,10 +678,7 @@
           <t>Heater (ISC)</t>
         </is>
       </c>
-      <c r="F9" t="b">
-        <v>1</v>
-      </c>
-      <c r="G9" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -735,10 +706,7 @@
           <t>Heater (ISC)</t>
         </is>
       </c>
-      <c r="F10" t="b">
-        <v>1</v>
-      </c>
-      <c r="G10" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -766,10 +734,7 @@
           <t>Heater (Non-ISC)</t>
         </is>
       </c>
-      <c r="F11" t="b">
-        <v>1</v>
-      </c>
-      <c r="G11" t="inlineStr">
+      <c r="F11" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -797,10 +762,7 @@
           <t>Heater (Non-ISC)</t>
         </is>
       </c>
-      <c r="F12" t="b">
-        <v>1</v>
-      </c>
-      <c r="G12" t="inlineStr">
+      <c r="F12" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -828,10 +790,7 @@
           <t>Heater (Non-ISC)</t>
         </is>
       </c>
-      <c r="F13" t="b">
-        <v>1</v>
-      </c>
-      <c r="G13" t="inlineStr">
+      <c r="F13" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -859,10 +818,7 @@
           <t>Heater (Non-ISC)</t>
         </is>
       </c>
-      <c r="F14" t="b">
-        <v>1</v>
-      </c>
-      <c r="G14" t="inlineStr">
+      <c r="F14" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -890,10 +846,7 @@
           <t>Heater (Non-ISC)</t>
         </is>
       </c>
-      <c r="F15" t="b">
-        <v>1</v>
-      </c>
-      <c r="G15" t="inlineStr">
+      <c r="F15" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -921,10 +874,7 @@
           <t>Heater (Non-ISC)</t>
         </is>
       </c>
-      <c r="F16" t="b">
-        <v>1</v>
-      </c>
-      <c r="G16" t="inlineStr">
+      <c r="F16" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -952,10 +902,7 @@
           <t>Heater (Non-ISC)</t>
         </is>
       </c>
-      <c r="F17" t="b">
-        <v>1</v>
-      </c>
-      <c r="G17" t="inlineStr">
+      <c r="F17" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -983,10 +930,7 @@
           <t>Heater (Non-ISC)</t>
         </is>
       </c>
-      <c r="F18" t="b">
-        <v>1</v>
-      </c>
-      <c r="G18" t="inlineStr">
+      <c r="F18" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -1014,10 +958,7 @@
           <t>Heater (Non-ISC)</t>
         </is>
       </c>
-      <c r="F19" t="b">
-        <v>0</v>
-      </c>
-      <c r="G19" t="inlineStr">
+      <c r="F19" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -1045,10 +986,7 @@
           <t>Heater (Non-ISC)</t>
         </is>
       </c>
-      <c r="F20" t="b">
-        <v>1</v>
-      </c>
-      <c r="G20" t="inlineStr">
+      <c r="F20" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -1076,10 +1014,7 @@
           <t>Nail</t>
         </is>
       </c>
-      <c r="F21" t="b">
-        <v>0</v>
-      </c>
-      <c r="G21" t="inlineStr">
+      <c r="F21" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -1107,10 +1042,7 @@
           <t>Nail</t>
         </is>
       </c>
-      <c r="F22" t="b">
-        <v>0</v>
-      </c>
-      <c r="G22" t="inlineStr">
+      <c r="F22" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -1138,10 +1070,7 @@
           <t>Nail</t>
         </is>
       </c>
-      <c r="F23" t="b">
-        <v>1</v>
-      </c>
-      <c r="G23" t="inlineStr">
+      <c r="F23" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -1169,10 +1098,7 @@
           <t>Heater (ISC)</t>
         </is>
       </c>
-      <c r="F24" t="b">
-        <v>1</v>
-      </c>
-      <c r="G24" t="inlineStr">
+      <c r="F24" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -1200,10 +1126,7 @@
           <t>Heater (ISC)</t>
         </is>
       </c>
-      <c r="F25" t="b">
-        <v>1</v>
-      </c>
-      <c r="G25" t="inlineStr">
+      <c r="F25" t="inlineStr">
         <is>
           <t>High</t>
         </is>
@@ -1231,10 +1154,7 @@
           <t>Heater (ISC)</t>
         </is>
       </c>
-      <c r="F26" t="b">
-        <v>1</v>
-      </c>
-      <c r="G26" t="inlineStr">
+      <c r="F26" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -1262,10 +1182,7 @@
           <t>Heater (ISC)</t>
         </is>
       </c>
-      <c r="F27" t="b">
-        <v>1</v>
-      </c>
-      <c r="G27" t="inlineStr">
+      <c r="F27" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -1293,10 +1210,7 @@
           <t>Heater (ISC)</t>
         </is>
       </c>
-      <c r="F28" t="b">
-        <v>1</v>
-      </c>
-      <c r="G28" t="inlineStr">
+      <c r="F28" t="inlineStr">
         <is>
           <t>High</t>
         </is>
@@ -1324,10 +1238,7 @@
           <t>Heater (ISC)</t>
         </is>
       </c>
-      <c r="F29" t="b">
-        <v>1</v>
-      </c>
-      <c r="G29" t="inlineStr">
+      <c r="F29" t="inlineStr">
         <is>
           <t>High</t>
         </is>
@@ -1355,10 +1266,7 @@
           <t>Heater (ISC)</t>
         </is>
       </c>
-      <c r="F30" t="b">
-        <v>1</v>
-      </c>
-      <c r="G30" t="inlineStr">
+      <c r="F30" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -1386,10 +1294,7 @@
           <t>Heater (ISC)</t>
         </is>
       </c>
-      <c r="F31" t="b">
-        <v>1</v>
-      </c>
-      <c r="G31" t="inlineStr">
+      <c r="F31" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -1417,10 +1322,7 @@
           <t>Heater (ISC)</t>
         </is>
       </c>
-      <c r="F32" t="b">
-        <v>1</v>
-      </c>
-      <c r="G32" t="inlineStr">
+      <c r="F32" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -1448,10 +1350,7 @@
           <t>Heater (ISC)</t>
         </is>
       </c>
-      <c r="F33" t="b">
-        <v>1</v>
-      </c>
-      <c r="G33" t="inlineStr">
+      <c r="F33" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -1479,10 +1378,7 @@
           <t>Heater (Non-ISC)</t>
         </is>
       </c>
-      <c r="F34" t="b">
-        <v>1</v>
-      </c>
-      <c r="G34" t="inlineStr">
+      <c r="F34" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -1510,10 +1406,7 @@
           <t>Heater (Non-ISC)</t>
         </is>
       </c>
-      <c r="F35" t="b">
-        <v>1</v>
-      </c>
-      <c r="G35" t="inlineStr">
+      <c r="F35" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -1541,10 +1434,7 @@
           <t>Heater (Non-ISC)</t>
         </is>
       </c>
-      <c r="F36" t="b">
-        <v>1</v>
-      </c>
-      <c r="G36" t="inlineStr">
+      <c r="F36" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -1572,10 +1462,7 @@
           <t>Heater (Non-ISC)</t>
         </is>
       </c>
-      <c r="F37" t="b">
-        <v>1</v>
-      </c>
-      <c r="G37" t="inlineStr">
+      <c r="F37" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -1603,10 +1490,7 @@
           <t>Heater (Non-ISC)</t>
         </is>
       </c>
-      <c r="F38" t="b">
-        <v>1</v>
-      </c>
-      <c r="G38" t="inlineStr">
+      <c r="F38" t="inlineStr">
         <is>
           <t>High</t>
         </is>
@@ -1634,10 +1518,7 @@
           <t>Heater (Non-ISC)</t>
         </is>
       </c>
-      <c r="F39" t="b">
-        <v>1</v>
-      </c>
-      <c r="G39" t="inlineStr">
+      <c r="F39" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -1665,10 +1546,7 @@
           <t>Heater (Non-ISC)</t>
         </is>
       </c>
-      <c r="F40" t="b">
-        <v>1</v>
-      </c>
-      <c r="G40" t="inlineStr">
+      <c r="F40" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -1696,10 +1574,7 @@
           <t>Heater (Non-ISC)</t>
         </is>
       </c>
-      <c r="F41" t="b">
-        <v>1</v>
-      </c>
-      <c r="G41" t="inlineStr">
+      <c r="F41" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -1727,10 +1602,7 @@
           <t>Nail</t>
         </is>
       </c>
-      <c r="F42" t="b">
-        <v>1</v>
-      </c>
-      <c r="G42" t="inlineStr">
+      <c r="F42" t="inlineStr">
         <is>
           <t>High</t>
         </is>
@@ -1758,10 +1630,7 @@
           <t>Nail</t>
         </is>
       </c>
-      <c r="F43" t="b">
-        <v>1</v>
-      </c>
-      <c r="G43" t="inlineStr">
+      <c r="F43" t="inlineStr">
         <is>
           <t>High</t>
         </is>
@@ -1789,10 +1658,7 @@
           <t>Nail</t>
         </is>
       </c>
-      <c r="F44" t="b">
-        <v>1</v>
-      </c>
-      <c r="G44" t="inlineStr">
+      <c r="F44" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -1820,10 +1686,7 @@
           <t>Nail</t>
         </is>
       </c>
-      <c r="F45" t="b">
-        <v>1</v>
-      </c>
-      <c r="G45" t="inlineStr">
+      <c r="F45" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -1851,10 +1714,7 @@
           <t>Nail</t>
         </is>
       </c>
-      <c r="F46" t="b">
-        <v>0</v>
-      </c>
-      <c r="G46" t="inlineStr">
+      <c r="F46" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -1882,10 +1742,7 @@
           <t>Nail</t>
         </is>
       </c>
-      <c r="F47" t="b">
-        <v>1</v>
-      </c>
-      <c r="G47" t="inlineStr">
+      <c r="F47" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -1913,10 +1770,7 @@
           <t>Nail</t>
         </is>
       </c>
-      <c r="F48" t="b">
-        <v>1</v>
-      </c>
-      <c r="G48" t="inlineStr">
+      <c r="F48" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -1944,10 +1798,7 @@
           <t>Nail</t>
         </is>
       </c>
-      <c r="F49" t="b">
-        <v>1</v>
-      </c>
-      <c r="G49" t="inlineStr">
+      <c r="F49" t="inlineStr">
         <is>
           <t>High</t>
         </is>
@@ -1975,10 +1826,7 @@
           <t>Nail</t>
         </is>
       </c>
-      <c r="F50" t="b">
-        <v>1</v>
-      </c>
-      <c r="G50" t="inlineStr">
+      <c r="F50" t="inlineStr">
         <is>
           <t>High</t>
         </is>
@@ -2006,10 +1854,7 @@
           <t>Nail</t>
         </is>
       </c>
-      <c r="F51" t="b">
-        <v>1</v>
-      </c>
-      <c r="G51" t="inlineStr">
+      <c r="F51" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -2037,10 +1882,7 @@
           <t>Nail</t>
         </is>
       </c>
-      <c r="F52" t="b">
-        <v>1</v>
-      </c>
-      <c r="G52" t="inlineStr">
+      <c r="F52" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -2068,10 +1910,7 @@
           <t>Nail</t>
         </is>
       </c>
-      <c r="F53" t="b">
-        <v>1</v>
-      </c>
-      <c r="G53" t="inlineStr">
+      <c r="F53" t="inlineStr">
         <is>
           <t>High</t>
         </is>
@@ -2099,10 +1938,7 @@
           <t>Heater (Non-ISC)</t>
         </is>
       </c>
-      <c r="F54" t="b">
-        <v>1</v>
-      </c>
-      <c r="G54" t="inlineStr">
+      <c r="F54" t="inlineStr">
         <is>
           <t>High</t>
         </is>
@@ -2130,10 +1966,7 @@
           <t>Heater (Non-ISC)</t>
         </is>
       </c>
-      <c r="F55" t="b">
-        <v>0</v>
-      </c>
-      <c r="G55" t="inlineStr">
+      <c r="F55" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -2161,10 +1994,7 @@
           <t>Heater (Non-ISC)</t>
         </is>
       </c>
-      <c r="F56" t="b">
-        <v>0</v>
-      </c>
-      <c r="G56" t="inlineStr">
+      <c r="F56" t="inlineStr">
         <is>
           <t>High</t>
         </is>
@@ -2192,10 +2022,7 @@
           <t>Heater (Non-ISC)</t>
         </is>
       </c>
-      <c r="F57" t="b">
-        <v>1</v>
-      </c>
-      <c r="G57" t="inlineStr">
+      <c r="F57" t="inlineStr">
         <is>
           <t>High</t>
         </is>
@@ -2223,10 +2050,7 @@
           <t>Heater (Non-ISC)</t>
         </is>
       </c>
-      <c r="F58" t="b">
-        <v>0</v>
-      </c>
-      <c r="G58" t="inlineStr">
+      <c r="F58" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -2254,10 +2078,7 @@
           <t>Heater (Non-ISC)</t>
         </is>
       </c>
-      <c r="F59" t="b">
-        <v>0</v>
-      </c>
-      <c r="G59" t="inlineStr">
+      <c r="F59" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -2285,10 +2106,7 @@
           <t>Heater (Non-ISC)</t>
         </is>
       </c>
-      <c r="F60" t="b">
-        <v>0</v>
-      </c>
-      <c r="G60" t="inlineStr">
+      <c r="F60" t="inlineStr">
         <is>
           <t>High</t>
         </is>
@@ -2316,10 +2134,7 @@
           <t>Heater (Non-ISC)</t>
         </is>
       </c>
-      <c r="F61" t="b">
-        <v>1</v>
-      </c>
-      <c r="G61" t="inlineStr">
+      <c r="F61" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -2347,10 +2162,7 @@
           <t>Heater (Non-ISC)</t>
         </is>
       </c>
-      <c r="F62" t="b">
-        <v>1</v>
-      </c>
-      <c r="G62" t="inlineStr">
+      <c r="F62" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -2378,10 +2190,7 @@
           <t>Heater (Non-ISC)</t>
         </is>
       </c>
-      <c r="F63" t="b">
-        <v>1</v>
-      </c>
-      <c r="G63" t="inlineStr">
+      <c r="F63" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -2409,10 +2218,7 @@
           <t>Heater (Non-ISC)</t>
         </is>
       </c>
-      <c r="F64" t="b">
-        <v>0</v>
-      </c>
-      <c r="G64" t="inlineStr">
+      <c r="F64" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -2440,10 +2246,7 @@
           <t>Nail</t>
         </is>
       </c>
-      <c r="F65" t="b">
-        <v>1</v>
-      </c>
-      <c r="G65" t="inlineStr">
+      <c r="F65" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -2471,10 +2274,7 @@
           <t>Nail</t>
         </is>
       </c>
-      <c r="F66" t="b">
-        <v>0</v>
-      </c>
-      <c r="G66" t="inlineStr">
+      <c r="F66" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -2502,10 +2302,7 @@
           <t>Heater (Non-ISC)</t>
         </is>
       </c>
-      <c r="F67" t="b">
-        <v>1</v>
-      </c>
-      <c r="G67" t="inlineStr">
+      <c r="F67" t="inlineStr">
         <is>
           <t>High</t>
         </is>
@@ -2533,10 +2330,7 @@
           <t>Heater (Non-ISC)</t>
         </is>
       </c>
-      <c r="F68" t="b">
-        <v>1</v>
-      </c>
-      <c r="G68" t="inlineStr">
+      <c r="F68" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -2564,10 +2358,7 @@
           <t>Heater (Non-ISC)</t>
         </is>
       </c>
-      <c r="F69" t="b">
-        <v>0</v>
-      </c>
-      <c r="G69" t="inlineStr">
+      <c r="F69" t="inlineStr">
         <is>
           <t>High</t>
         </is>
@@ -2595,10 +2386,7 @@
           <t>Heater (Non-ISC)</t>
         </is>
       </c>
-      <c r="F70" t="b">
-        <v>0</v>
-      </c>
-      <c r="G70" t="inlineStr">
+      <c r="F70" t="inlineStr">
         <is>
           <t>High</t>
         </is>
@@ -2626,10 +2414,7 @@
           <t>Heater (Non-ISC)</t>
         </is>
       </c>
-      <c r="F71" t="b">
-        <v>0</v>
-      </c>
-      <c r="G71" t="inlineStr">
+      <c r="F71" t="inlineStr">
         <is>
           <t>High</t>
         </is>
@@ -2657,10 +2442,7 @@
           <t>Heater (Non-ISC)</t>
         </is>
       </c>
-      <c r="F72" t="b">
-        <v>0</v>
-      </c>
-      <c r="G72" t="inlineStr">
+      <c r="F72" t="inlineStr">
         <is>
           <t>High</t>
         </is>
@@ -2688,10 +2470,7 @@
           <t>Heater (Non-ISC)</t>
         </is>
       </c>
-      <c r="F73" t="b">
-        <v>0</v>
-      </c>
-      <c r="G73" t="inlineStr">
+      <c r="F73" t="inlineStr">
         <is>
           <t>High</t>
         </is>
@@ -2719,10 +2498,7 @@
           <t>Heater (Non-ISC)</t>
         </is>
       </c>
-      <c r="F74" t="b">
-        <v>0</v>
-      </c>
-      <c r="G74" t="inlineStr">
+      <c r="F74" t="inlineStr">
         <is>
           <t>High</t>
         </is>
@@ -2750,10 +2526,7 @@
           <t>Heater (Non-ISC)</t>
         </is>
       </c>
-      <c r="F75" t="b">
-        <v>1</v>
-      </c>
-      <c r="G75" t="inlineStr">
+      <c r="F75" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -2781,10 +2554,7 @@
           <t>Heater (Non-ISC)</t>
         </is>
       </c>
-      <c r="F76" t="b">
-        <v>0</v>
-      </c>
-      <c r="G76" t="inlineStr">
+      <c r="F76" t="inlineStr">
         <is>
           <t>High</t>
         </is>
@@ -2812,10 +2582,7 @@
           <t>Heater (Non-ISC)</t>
         </is>
       </c>
-      <c r="F77" t="b">
-        <v>0</v>
-      </c>
-      <c r="G77" t="inlineStr">
+      <c r="F77" t="inlineStr">
         <is>
           <t>High</t>
         </is>
@@ -2843,10 +2610,7 @@
           <t>Heater (Non-ISC)</t>
         </is>
       </c>
-      <c r="F78" t="b">
-        <v>0</v>
-      </c>
-      <c r="G78" t="inlineStr">
+      <c r="F78" t="inlineStr">
         <is>
           <t>High</t>
         </is>
@@ -2874,10 +2638,7 @@
           <t>Heater (Non-ISC)</t>
         </is>
       </c>
-      <c r="F79" t="b">
-        <v>0</v>
-      </c>
-      <c r="G79" t="inlineStr">
+      <c r="F79" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -2905,10 +2666,7 @@
           <t>Heater (Non-ISC)</t>
         </is>
       </c>
-      <c r="F80" t="b">
-        <v>0</v>
-      </c>
-      <c r="G80" t="inlineStr">
+      <c r="F80" t="inlineStr">
         <is>
           <t>High</t>
         </is>
@@ -2936,10 +2694,7 @@
           <t>Heater (Non-ISC)</t>
         </is>
       </c>
-      <c r="F81" t="b">
-        <v>0</v>
-      </c>
-      <c r="G81" t="inlineStr">
+      <c r="F81" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -2967,10 +2722,7 @@
           <t>Heater (ISC)</t>
         </is>
       </c>
-      <c r="F82" t="b">
-        <v>0</v>
-      </c>
-      <c r="G82" t="inlineStr">
+      <c r="F82" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -2998,10 +2750,7 @@
           <t>Heater (ISC)</t>
         </is>
       </c>
-      <c r="F83" t="b">
-        <v>1</v>
-      </c>
-      <c r="G83" t="inlineStr">
+      <c r="F83" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -3029,10 +2778,7 @@
           <t>Heater (ISC)</t>
         </is>
       </c>
-      <c r="F84" t="b">
-        <v>1</v>
-      </c>
-      <c r="G84" t="inlineStr">
+      <c r="F84" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -3060,10 +2806,7 @@
           <t>Heater (ISC)</t>
         </is>
       </c>
-      <c r="F85" t="b">
-        <v>0</v>
-      </c>
-      <c r="G85" t="inlineStr">
+      <c r="F85" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -3091,10 +2834,7 @@
           <t>Heater (ISC)</t>
         </is>
       </c>
-      <c r="F86" t="b">
-        <v>1</v>
-      </c>
-      <c r="G86" t="inlineStr">
+      <c r="F86" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -3122,10 +2862,7 @@
           <t>Heater (ISC)</t>
         </is>
       </c>
-      <c r="F87" t="b">
-        <v>1</v>
-      </c>
-      <c r="G87" t="inlineStr">
+      <c r="F87" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -3153,10 +2890,7 @@
           <t>Heater (ISC)</t>
         </is>
       </c>
-      <c r="F88" t="b">
-        <v>1</v>
-      </c>
-      <c r="G88" t="inlineStr">
+      <c r="F88" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -3184,10 +2918,7 @@
           <t>Heater (ISC)</t>
         </is>
       </c>
-      <c r="F89" t="b">
-        <v>0</v>
-      </c>
-      <c r="G89" t="inlineStr">
+      <c r="F89" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -3215,10 +2946,7 @@
           <t>Heater (ISC)</t>
         </is>
       </c>
-      <c r="F90" t="b">
-        <v>1</v>
-      </c>
-      <c r="G90" t="inlineStr">
+      <c r="F90" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -3246,10 +2974,7 @@
           <t>Heater (ISC)</t>
         </is>
       </c>
-      <c r="F91" t="b">
-        <v>1</v>
-      </c>
-      <c r="G91" t="inlineStr">
+      <c r="F91" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -3277,10 +3002,7 @@
           <t>Heater (ISC)</t>
         </is>
       </c>
-      <c r="F92" t="b">
-        <v>0</v>
-      </c>
-      <c r="G92" t="inlineStr">
+      <c r="F92" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -3308,10 +3030,7 @@
           <t>Heater (ISC)</t>
         </is>
       </c>
-      <c r="F93" t="b">
-        <v>1</v>
-      </c>
-      <c r="G93" t="inlineStr">
+      <c r="F93" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -3339,10 +3058,7 @@
           <t>Heater (Non-ISC)</t>
         </is>
       </c>
-      <c r="F94" t="b">
-        <v>1</v>
-      </c>
-      <c r="G94" t="inlineStr">
+      <c r="F94" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -3370,10 +3086,7 @@
           <t>Heater (Non-ISC)</t>
         </is>
       </c>
-      <c r="F95" t="b">
-        <v>1</v>
-      </c>
-      <c r="G95" t="inlineStr">
+      <c r="F95" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -3401,10 +3114,7 @@
           <t>Heater (Non-ISC)</t>
         </is>
       </c>
-      <c r="F96" t="b">
-        <v>1</v>
-      </c>
-      <c r="G96" t="inlineStr">
+      <c r="F96" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -3432,10 +3142,7 @@
           <t>Heater (Non-ISC)</t>
         </is>
       </c>
-      <c r="F97" t="b">
-        <v>1</v>
-      </c>
-      <c r="G97" t="inlineStr">
+      <c r="F97" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -3463,10 +3170,7 @@
           <t>Heater (ISC)</t>
         </is>
       </c>
-      <c r="F98" t="b">
-        <v>1</v>
-      </c>
-      <c r="G98" t="inlineStr">
+      <c r="F98" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -3494,10 +3198,7 @@
           <t>Heater (ISC)</t>
         </is>
       </c>
-      <c r="F99" t="b">
-        <v>1</v>
-      </c>
-      <c r="G99" t="inlineStr">
+      <c r="F99" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -3525,10 +3226,7 @@
           <t>Heater (ISC)</t>
         </is>
       </c>
-      <c r="F100" t="b">
-        <v>1</v>
-      </c>
-      <c r="G100" t="inlineStr">
+      <c r="F100" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -3556,10 +3254,7 @@
           <t>Heater (ISC)</t>
         </is>
       </c>
-      <c r="F101" t="b">
-        <v>1</v>
-      </c>
-      <c r="G101" t="inlineStr">
+      <c r="F101" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -3587,10 +3282,7 @@
           <t>Heater (ISC)</t>
         </is>
       </c>
-      <c r="F102" t="b">
-        <v>1</v>
-      </c>
-      <c r="G102" t="inlineStr">
+      <c r="F102" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -3618,10 +3310,7 @@
           <t>Heater (ISC)</t>
         </is>
       </c>
-      <c r="F103" t="b">
-        <v>1</v>
-      </c>
-      <c r="G103" t="inlineStr">
+      <c r="F103" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -3649,10 +3338,7 @@
           <t>Heater (ISC)</t>
         </is>
       </c>
-      <c r="F104" t="b">
-        <v>1</v>
-      </c>
-      <c r="G104" t="inlineStr">
+      <c r="F104" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -3680,10 +3366,7 @@
           <t>Heater (ISC)</t>
         </is>
       </c>
-      <c r="F105" t="b">
-        <v>0</v>
-      </c>
-      <c r="G105" t="inlineStr">
+      <c r="F105" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -3711,10 +3394,7 @@
           <t>Heater (ISC)</t>
         </is>
       </c>
-      <c r="F106" t="b">
-        <v>1</v>
-      </c>
-      <c r="G106" t="inlineStr">
+      <c r="F106" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -3742,10 +3422,7 @@
           <t>Heater (ISC)</t>
         </is>
       </c>
-      <c r="F107" t="b">
-        <v>1</v>
-      </c>
-      <c r="G107" t="inlineStr">
+      <c r="F107" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -3773,10 +3450,7 @@
           <t>Heater (ISC)</t>
         </is>
       </c>
-      <c r="F108" t="b">
-        <v>1</v>
-      </c>
-      <c r="G108" t="inlineStr">
+      <c r="F108" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -3804,10 +3478,7 @@
           <t>Heater (ISC)</t>
         </is>
       </c>
-      <c r="F109" t="b">
-        <v>1</v>
-      </c>
-      <c r="G109" t="inlineStr">
+      <c r="F109" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -3835,10 +3506,7 @@
           <t>Heater (ISC)</t>
         </is>
       </c>
-      <c r="F110" t="b">
-        <v>1</v>
-      </c>
-      <c r="G110" t="inlineStr">
+      <c r="F110" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -3866,10 +3534,7 @@
           <t>Heater (ISC)</t>
         </is>
       </c>
-      <c r="F111" t="b">
-        <v>1</v>
-      </c>
-      <c r="G111" t="inlineStr">
+      <c r="F111" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -3897,10 +3562,7 @@
           <t>Heater (ISC)</t>
         </is>
       </c>
-      <c r="F112" t="b">
-        <v>0</v>
-      </c>
-      <c r="G112" t="inlineStr">
+      <c r="F112" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -3928,10 +3590,7 @@
           <t>Heater (ISC)</t>
         </is>
       </c>
-      <c r="F113" t="b">
-        <v>1</v>
-      </c>
-      <c r="G113" t="inlineStr">
+      <c r="F113" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -3959,10 +3618,7 @@
           <t>Heater (Non-ISC)</t>
         </is>
       </c>
-      <c r="F114" t="b">
-        <v>0</v>
-      </c>
-      <c r="G114" t="inlineStr">
+      <c r="F114" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -3990,10 +3646,7 @@
           <t>Heater (Non-ISC)</t>
         </is>
       </c>
-      <c r="F115" t="b">
-        <v>0</v>
-      </c>
-      <c r="G115" t="inlineStr">
+      <c r="F115" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -4021,10 +3674,7 @@
           <t>Heater (Non-ISC)</t>
         </is>
       </c>
-      <c r="F116" t="b">
-        <v>1</v>
-      </c>
-      <c r="G116" t="inlineStr">
+      <c r="F116" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -4052,10 +3702,7 @@
           <t>Heater (Non-ISC)</t>
         </is>
       </c>
-      <c r="F117" t="b">
-        <v>0</v>
-      </c>
-      <c r="G117" t="inlineStr">
+      <c r="F117" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -4083,10 +3730,7 @@
           <t>Heater (ISC)</t>
         </is>
       </c>
-      <c r="F118" t="b">
-        <v>0</v>
-      </c>
-      <c r="G118" t="inlineStr">
+      <c r="F118" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -4114,10 +3758,7 @@
           <t>Heater (ISC)</t>
         </is>
       </c>
-      <c r="F119" t="b">
-        <v>0</v>
-      </c>
-      <c r="G119" t="inlineStr">
+      <c r="F119" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -4145,10 +3786,7 @@
           <t>Heater (ISC)</t>
         </is>
       </c>
-      <c r="F120" t="b">
-        <v>0</v>
-      </c>
-      <c r="G120" t="inlineStr">
+      <c r="F120" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -4176,10 +3814,7 @@
           <t>Heater (ISC)</t>
         </is>
       </c>
-      <c r="F121" t="b">
-        <v>0</v>
-      </c>
-      <c r="G121" t="inlineStr">
+      <c r="F121" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -4207,10 +3842,7 @@
           <t>Heater (ISC)</t>
         </is>
       </c>
-      <c r="F122" t="b">
-        <v>0</v>
-      </c>
-      <c r="G122" t="inlineStr">
+      <c r="F122" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -4238,10 +3870,7 @@
           <t>Heater (ISC)</t>
         </is>
       </c>
-      <c r="F123" t="b">
-        <v>0</v>
-      </c>
-      <c r="G123" t="inlineStr">
+      <c r="F123" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -4269,10 +3898,7 @@
           <t>Heater (ISC)</t>
         </is>
       </c>
-      <c r="F124" t="b">
-        <v>0</v>
-      </c>
-      <c r="G124" t="inlineStr">
+      <c r="F124" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -4300,10 +3926,7 @@
           <t>Heater (ISC)</t>
         </is>
       </c>
-      <c r="F125" t="b">
-        <v>1</v>
-      </c>
-      <c r="G125" t="inlineStr">
+      <c r="F125" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -4331,10 +3954,7 @@
           <t>Heater (ISC)</t>
         </is>
       </c>
-      <c r="F126" t="b">
-        <v>1</v>
-      </c>
-      <c r="G126" t="inlineStr">
+      <c r="F126" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -4362,10 +3982,7 @@
           <t>Heater (ISC)</t>
         </is>
       </c>
-      <c r="F127" t="b">
-        <v>0</v>
-      </c>
-      <c r="G127" t="inlineStr">
+      <c r="F127" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -4393,10 +4010,7 @@
           <t>Heater (ISC)</t>
         </is>
       </c>
-      <c r="F128" t="b">
-        <v>0</v>
-      </c>
-      <c r="G128" t="inlineStr">
+      <c r="F128" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -4417,17 +4031,14 @@
         <v>21700</v>
       </c>
       <c r="D129" t="n">
-        <v>5.013774104683195</v>
+        <v>5.0137741046832</v>
       </c>
       <c r="E129" t="inlineStr">
         <is>
           <t>Heater (Non-ISC)</t>
         </is>
       </c>
-      <c r="F129" t="b">
-        <v>1</v>
-      </c>
-      <c r="G129" t="inlineStr">
+      <c r="F129" t="inlineStr">
         <is>
           <t>High</t>
         </is>
@@ -4448,17 +4059,14 @@
         <v>21700</v>
       </c>
       <c r="D130" t="n">
-        <v>5.013774104683195</v>
+        <v>5.0137741046832</v>
       </c>
       <c r="E130" t="inlineStr">
         <is>
           <t>Heater (Non-ISC)</t>
         </is>
       </c>
-      <c r="F130" t="b">
-        <v>1</v>
-      </c>
-      <c r="G130" t="inlineStr">
+      <c r="F130" t="inlineStr">
         <is>
           <t>High</t>
         </is>
@@ -4479,17 +4087,14 @@
         <v>21700</v>
       </c>
       <c r="D131" t="n">
-        <v>5.013774104683195</v>
+        <v>5.0137741046832</v>
       </c>
       <c r="E131" t="inlineStr">
         <is>
           <t>Heater (Non-ISC)</t>
         </is>
       </c>
-      <c r="F131" t="b">
-        <v>1</v>
-      </c>
-      <c r="G131" t="inlineStr">
+      <c r="F131" t="inlineStr">
         <is>
           <t>High</t>
         </is>
@@ -4510,17 +4115,14 @@
         <v>21700</v>
       </c>
       <c r="D132" t="n">
-        <v>5.013774104683195</v>
+        <v>5.0137741046832</v>
       </c>
       <c r="E132" t="inlineStr">
         <is>
           <t>Heater (Non-ISC)</t>
         </is>
       </c>
-      <c r="F132" t="b">
-        <v>1</v>
-      </c>
-      <c r="G132" t="inlineStr">
+      <c r="F132" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -4541,17 +4143,14 @@
         <v>21700</v>
       </c>
       <c r="D133" t="n">
-        <v>5.013774104683195</v>
+        <v>5.0137741046832</v>
       </c>
       <c r="E133" t="inlineStr">
         <is>
           <t>Heater (Non-ISC)</t>
         </is>
       </c>
-      <c r="F133" t="b">
-        <v>1</v>
-      </c>
-      <c r="G133" t="inlineStr">
+      <c r="F133" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -4572,17 +4171,14 @@
         <v>21700</v>
       </c>
       <c r="D134" t="n">
-        <v>5.013774104683195</v>
+        <v>5.0137741046832</v>
       </c>
       <c r="E134" t="inlineStr">
         <is>
           <t>Heater (Non-ISC)</t>
         </is>
       </c>
-      <c r="F134" t="b">
-        <v>1</v>
-      </c>
-      <c r="G134" t="inlineStr">
+      <c r="F134" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -4603,17 +4199,14 @@
         <v>21700</v>
       </c>
       <c r="D135" t="n">
-        <v>5.013774104683195</v>
+        <v>5.0137741046832</v>
       </c>
       <c r="E135" t="inlineStr">
         <is>
           <t>Heater (Non-ISC)</t>
         </is>
       </c>
-      <c r="F135" t="b">
-        <v>1</v>
-      </c>
-      <c r="G135" t="inlineStr">
+      <c r="F135" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -4634,17 +4227,14 @@
         <v>21700</v>
       </c>
       <c r="D136" t="n">
-        <v>5.013774104683195</v>
+        <v>5.0137741046832</v>
       </c>
       <c r="E136" t="inlineStr">
         <is>
           <t>Heater (Non-ISC)</t>
         </is>
       </c>
-      <c r="F136" t="b">
-        <v>1</v>
-      </c>
-      <c r="G136" t="inlineStr">
+      <c r="F136" t="inlineStr">
         <is>
           <t>High</t>
         </is>
@@ -4665,17 +4255,14 @@
         <v>21700</v>
       </c>
       <c r="D137" t="n">
-        <v>5.013774104683195</v>
+        <v>5.0137741046832</v>
       </c>
       <c r="E137" t="inlineStr">
         <is>
           <t>Nail</t>
         </is>
       </c>
-      <c r="F137" t="b">
-        <v>1</v>
-      </c>
-      <c r="G137" t="inlineStr">
+      <c r="F137" t="inlineStr">
         <is>
           <t>High</t>
         </is>
@@ -4696,17 +4283,14 @@
         <v>21700</v>
       </c>
       <c r="D138" t="n">
-        <v>5.013774104683195</v>
+        <v>5.0137741046832</v>
       </c>
       <c r="E138" t="inlineStr">
         <is>
           <t>Nail</t>
         </is>
       </c>
-      <c r="F138" t="b">
-        <v>1</v>
-      </c>
-      <c r="G138" t="inlineStr">
+      <c r="F138" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -4727,17 +4311,14 @@
         <v>21700</v>
       </c>
       <c r="D139" t="n">
-        <v>5.013774104683195</v>
+        <v>5.0137741046832</v>
       </c>
       <c r="E139" t="inlineStr">
         <is>
           <t>Nail</t>
         </is>
       </c>
-      <c r="F139" t="b">
-        <v>1</v>
-      </c>
-      <c r="G139" t="inlineStr">
+      <c r="F139" t="inlineStr">
         <is>
           <t>High</t>
         </is>
@@ -4758,17 +4339,14 @@
         <v>21700</v>
       </c>
       <c r="D140" t="n">
-        <v>5.013774104683195</v>
+        <v>5.0137741046832</v>
       </c>
       <c r="E140" t="inlineStr">
         <is>
           <t>Nail</t>
         </is>
       </c>
-      <c r="F140" t="b">
-        <v>1</v>
-      </c>
-      <c r="G140" t="inlineStr">
+      <c r="F140" t="inlineStr">
         <is>
           <t>High</t>
         </is>
@@ -4789,17 +4367,14 @@
         <v>21700</v>
       </c>
       <c r="D141" t="n">
-        <v>5.013774104683195</v>
+        <v>5.0137741046832</v>
       </c>
       <c r="E141" t="inlineStr">
         <is>
           <t>Nail</t>
         </is>
       </c>
-      <c r="F141" t="b">
-        <v>1</v>
-      </c>
-      <c r="G141" t="inlineStr">
+      <c r="F141" t="inlineStr">
         <is>
           <t>High</t>
         </is>
@@ -4820,17 +4395,14 @@
         <v>21700</v>
       </c>
       <c r="D142" t="n">
-        <v>5.013774104683195</v>
+        <v>5.0137741046832</v>
       </c>
       <c r="E142" t="inlineStr">
         <is>
           <t>Nail</t>
         </is>
       </c>
-      <c r="F142" t="b">
-        <v>1</v>
-      </c>
-      <c r="G142" t="inlineStr">
+      <c r="F142" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -4851,17 +4423,14 @@
         <v>21700</v>
       </c>
       <c r="D143" t="n">
-        <v>5.013774104683195</v>
+        <v>5.0137741046832</v>
       </c>
       <c r="E143" t="inlineStr">
         <is>
           <t>Nail</t>
         </is>
       </c>
-      <c r="F143" t="b">
-        <v>0</v>
-      </c>
-      <c r="G143" t="inlineStr">
+      <c r="F143" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -4882,17 +4451,14 @@
         <v>21700</v>
       </c>
       <c r="D144" t="n">
-        <v>5.013774104683195</v>
+        <v>5.0137741046832</v>
       </c>
       <c r="E144" t="inlineStr">
         <is>
           <t>Nail</t>
         </is>
       </c>
-      <c r="F144" t="b">
-        <v>0</v>
-      </c>
-      <c r="G144" t="inlineStr">
+      <c r="F144" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -4913,17 +4479,14 @@
         <v>21700</v>
       </c>
       <c r="D145" t="n">
-        <v>5.013774104683195</v>
+        <v>5.0137741046832</v>
       </c>
       <c r="E145" t="inlineStr">
         <is>
           <t>Nail</t>
         </is>
       </c>
-      <c r="F145" t="b">
-        <v>0</v>
-      </c>
-      <c r="G145" t="inlineStr">
+      <c r="F145" t="inlineStr">
         <is>
           <t>High</t>
         </is>
@@ -4944,17 +4507,14 @@
         <v>21700</v>
       </c>
       <c r="D146" t="n">
-        <v>5.013774104683195</v>
+        <v>5.0137741046832</v>
       </c>
       <c r="E146" t="inlineStr">
         <is>
           <t>Nail</t>
         </is>
       </c>
-      <c r="F146" t="b">
-        <v>0</v>
-      </c>
-      <c r="G146" t="inlineStr">
+      <c r="F146" t="inlineStr">
         <is>
           <t>High</t>
         </is>
@@ -4982,10 +4542,7 @@
           <t>Heater (Non-ISC)</t>
         </is>
       </c>
-      <c r="F147" t="b">
-        <v>0</v>
-      </c>
-      <c r="G147" t="inlineStr">
+      <c r="F147" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -5013,10 +4570,7 @@
           <t>Heater (Non-ISC)</t>
         </is>
       </c>
-      <c r="F148" t="b">
-        <v>0</v>
-      </c>
-      <c r="G148" t="inlineStr">
+      <c r="F148" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -5044,10 +4598,7 @@
           <t>Heater (Non-ISC)</t>
         </is>
       </c>
-      <c r="F149" t="b">
-        <v>0</v>
-      </c>
-      <c r="G149" t="inlineStr">
+      <c r="F149" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -5075,10 +4626,7 @@
           <t>Heater (Non-ISC)</t>
         </is>
       </c>
-      <c r="F150" t="b">
-        <v>0</v>
-      </c>
-      <c r="G150" t="inlineStr">
+      <c r="F150" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -5106,10 +4654,7 @@
           <t>Heater (Non-ISC)</t>
         </is>
       </c>
-      <c r="F151" t="b">
-        <v>0</v>
-      </c>
-      <c r="G151" t="inlineStr">
+      <c r="F151" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -5137,10 +4682,7 @@
           <t>Heater (Non-ISC)</t>
         </is>
       </c>
-      <c r="F152" t="b">
-        <v>0</v>
-      </c>
-      <c r="G152" t="inlineStr">
+      <c r="F152" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -5168,10 +4710,7 @@
           <t>Heater (Non-ISC)</t>
         </is>
       </c>
-      <c r="F153" t="b">
-        <v>1</v>
-      </c>
-      <c r="G153" t="inlineStr">
+      <c r="F153" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -5199,10 +4738,7 @@
           <t>Heater (Non-ISC)</t>
         </is>
       </c>
-      <c r="F154" t="b">
-        <v>0</v>
-      </c>
-      <c r="G154" t="inlineStr">
+      <c r="F154" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -5230,10 +4766,7 @@
           <t>Heater (Non-ISC)</t>
         </is>
       </c>
-      <c r="F155" t="b">
-        <v>0</v>
-      </c>
-      <c r="G155" t="inlineStr">
+      <c r="F155" t="inlineStr">
         <is>
           <t>High</t>
         </is>
@@ -5261,10 +4794,7 @@
           <t>Heater (Non-ISC)</t>
         </is>
       </c>
-      <c r="F156" t="b">
-        <v>1</v>
-      </c>
-      <c r="G156" t="inlineStr">
+      <c r="F156" t="inlineStr">
         <is>
           <t>High</t>
         </is>
@@ -5292,10 +4822,7 @@
           <t>Heater (Non-ISC)</t>
         </is>
       </c>
-      <c r="F157" t="b">
-        <v>0</v>
-      </c>
-      <c r="G157" t="inlineStr">
+      <c r="F157" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -5323,10 +4850,7 @@
           <t>Heater (Non-ISC)</t>
         </is>
       </c>
-      <c r="F158" t="b">
-        <v>0</v>
-      </c>
-      <c r="G158" t="inlineStr">
+      <c r="F158" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -5354,10 +4878,7 @@
           <t>Heater (Non-ISC)</t>
         </is>
       </c>
-      <c r="F159" t="b">
-        <v>0</v>
-      </c>
-      <c r="G159" t="inlineStr">
+      <c r="F159" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -5385,10 +4906,7 @@
           <t>Heater (Non-ISC)</t>
         </is>
       </c>
-      <c r="F160" t="b">
-        <v>1</v>
-      </c>
-      <c r="G160" t="inlineStr">
+      <c r="F160" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -5416,10 +4934,7 @@
           <t>Nail</t>
         </is>
       </c>
-      <c r="F161" t="b">
-        <v>0</v>
-      </c>
-      <c r="G161" t="inlineStr">
+      <c r="F161" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -5447,10 +4962,7 @@
           <t>Nail</t>
         </is>
       </c>
-      <c r="F162" t="b">
-        <v>0</v>
-      </c>
-      <c r="G162" t="inlineStr">
+      <c r="F162" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -5478,10 +4990,7 @@
           <t>Nail</t>
         </is>
       </c>
-      <c r="F163" t="b">
-        <v>0</v>
-      </c>
-      <c r="G163" t="inlineStr">
+      <c r="F163" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -5509,10 +5018,7 @@
           <t>Nail</t>
         </is>
       </c>
-      <c r="F164" t="b">
-        <v>0</v>
-      </c>
-      <c r="G164" t="inlineStr">
+      <c r="F164" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -5540,10 +5046,7 @@
           <t>Nail</t>
         </is>
       </c>
-      <c r="F165" t="b">
-        <v>0</v>
-      </c>
-      <c r="G165" t="inlineStr">
+      <c r="F165" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -5571,10 +5074,7 @@
           <t>Nail</t>
         </is>
       </c>
-      <c r="F166" t="b">
-        <v>0</v>
-      </c>
-      <c r="G166" t="inlineStr">
+      <c r="F166" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -5602,10 +5102,7 @@
           <t>Nail</t>
         </is>
       </c>
-      <c r="F167" t="b">
-        <v>0</v>
-      </c>
-      <c r="G167" t="inlineStr">
+      <c r="F167" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -5633,10 +5130,7 @@
           <t>Nail</t>
         </is>
       </c>
-      <c r="F168" t="b">
-        <v>0</v>
-      </c>
-      <c r="G168" t="inlineStr">
+      <c r="F168" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -5664,10 +5158,7 @@
           <t>Nail</t>
         </is>
       </c>
-      <c r="F169" t="b">
-        <v>0</v>
-      </c>
-      <c r="G169" t="inlineStr">
+      <c r="F169" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -5695,10 +5186,7 @@
           <t>Nail</t>
         </is>
       </c>
-      <c r="F170" t="b">
-        <v>0</v>
-      </c>
-      <c r="G170" t="inlineStr">
+      <c r="F170" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -5726,10 +5214,7 @@
           <t>Heater (ISC)</t>
         </is>
       </c>
-      <c r="F171" t="b">
-        <v>0</v>
-      </c>
-      <c r="G171" t="inlineStr">
+      <c r="F171" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -5757,10 +5242,7 @@
           <t>Heater (ISC)</t>
         </is>
       </c>
-      <c r="F172" t="b">
-        <v>0</v>
-      </c>
-      <c r="G172" t="inlineStr">
+      <c r="F172" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -5788,10 +5270,7 @@
           <t>Heater (ISC)</t>
         </is>
       </c>
-      <c r="F173" t="b">
-        <v>0</v>
-      </c>
-      <c r="G173" t="inlineStr">
+      <c r="F173" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -5819,10 +5298,7 @@
           <t>Heater (ISC)</t>
         </is>
       </c>
-      <c r="F174" t="b">
-        <v>0</v>
-      </c>
-      <c r="G174" t="inlineStr">
+      <c r="F174" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -5850,10 +5326,7 @@
           <t>Heater (ISC)</t>
         </is>
       </c>
-      <c r="F175" t="b">
-        <v>0</v>
-      </c>
-      <c r="G175" t="inlineStr">
+      <c r="F175" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -5881,10 +5354,7 @@
           <t>Heater (ISC)</t>
         </is>
       </c>
-      <c r="F176" t="b">
-        <v>0</v>
-      </c>
-      <c r="G176" t="inlineStr">
+      <c r="F176" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -5912,10 +5382,7 @@
           <t>Heater (ISC)</t>
         </is>
       </c>
-      <c r="F177" t="b">
-        <v>0</v>
-      </c>
-      <c r="G177" t="inlineStr">
+      <c r="F177" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -5943,10 +5410,7 @@
           <t>Heater (Non-ISC)</t>
         </is>
       </c>
-      <c r="F178" t="b">
-        <v>1</v>
-      </c>
-      <c r="G178" t="inlineStr">
+      <c r="F178" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -5974,10 +5438,7 @@
           <t>Heater (Non-ISC)</t>
         </is>
       </c>
-      <c r="F179" t="b">
-        <v>1</v>
-      </c>
-      <c r="G179" t="inlineStr">
+      <c r="F179" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -6005,10 +5466,7 @@
           <t>Heater (ISC)</t>
         </is>
       </c>
-      <c r="F180" t="b">
-        <v>0</v>
-      </c>
-      <c r="G180" t="inlineStr">
+      <c r="F180" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -6036,10 +5494,7 @@
           <t>Heater (ISC)</t>
         </is>
       </c>
-      <c r="F181" t="b">
-        <v>0</v>
-      </c>
-      <c r="G181" t="inlineStr">
+      <c r="F181" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -6067,10 +5522,7 @@
           <t>Heater (ISC)</t>
         </is>
       </c>
-      <c r="F182" t="b">
-        <v>0</v>
-      </c>
-      <c r="G182" t="inlineStr">
+      <c r="F182" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -6098,10 +5550,7 @@
           <t>Heater (ISC)</t>
         </is>
       </c>
-      <c r="F183" t="b">
-        <v>0</v>
-      </c>
-      <c r="G183" t="inlineStr">
+      <c r="F183" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -6129,10 +5578,7 @@
           <t>Heater (ISC)</t>
         </is>
       </c>
-      <c r="F184" t="b">
-        <v>0</v>
-      </c>
-      <c r="G184" t="inlineStr">
+      <c r="F184" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -6160,10 +5606,7 @@
           <t>Heater (ISC)</t>
         </is>
       </c>
-      <c r="F185" t="b">
-        <v>0</v>
-      </c>
-      <c r="G185" t="inlineStr">
+      <c r="F185" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -6191,10 +5634,7 @@
           <t>Heater (ISC)</t>
         </is>
       </c>
-      <c r="F186" t="b">
-        <v>0</v>
-      </c>
-      <c r="G186" t="inlineStr">
+      <c r="F186" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -6222,10 +5662,7 @@
           <t>Heater (ISC)</t>
         </is>
       </c>
-      <c r="F187" t="b">
-        <v>0</v>
-      </c>
-      <c r="G187" t="inlineStr">
+      <c r="F187" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -6253,10 +5690,7 @@
           <t>Heater (ISC)</t>
         </is>
       </c>
-      <c r="F188" t="b">
-        <v>0</v>
-      </c>
-      <c r="G188" t="inlineStr">
+      <c r="F188" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -6284,10 +5718,7 @@
           <t>Heater (Non-ISC)</t>
         </is>
       </c>
-      <c r="F189" t="b">
-        <v>0</v>
-      </c>
-      <c r="G189" t="inlineStr">
+      <c r="F189" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -6315,10 +5746,7 @@
           <t>Heater (Non-ISC)</t>
         </is>
       </c>
-      <c r="F190" t="b">
-        <v>0</v>
-      </c>
-      <c r="G190" t="inlineStr">
+      <c r="F190" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -6346,10 +5774,7 @@
           <t>Heater (Non-ISC)</t>
         </is>
       </c>
-      <c r="F191" t="b">
-        <v>0</v>
-      </c>
-      <c r="G191" t="inlineStr">
+      <c r="F191" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -6377,10 +5802,7 @@
           <t>Heater (Non-ISC)</t>
         </is>
       </c>
-      <c r="F192" t="b">
-        <v>0</v>
-      </c>
-      <c r="G192" t="inlineStr">
+      <c r="F192" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -6408,10 +5830,7 @@
           <t>Heater (Non-ISC)</t>
         </is>
       </c>
-      <c r="F193" t="b">
-        <v>0</v>
-      </c>
-      <c r="G193" t="inlineStr">
+      <c r="F193" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -6439,10 +5858,7 @@
           <t>Heater (Non-ISC)</t>
         </is>
       </c>
-      <c r="F194" t="b">
-        <v>0</v>
-      </c>
-      <c r="G194" t="inlineStr">
+      <c r="F194" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -6470,10 +5886,7 @@
           <t>Heater (Non-ISC)</t>
         </is>
       </c>
-      <c r="F195" t="b">
-        <v>0</v>
-      </c>
-      <c r="G195" t="inlineStr">
+      <c r="F195" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -6501,10 +5914,7 @@
           <t>Heater (Non-ISC)</t>
         </is>
       </c>
-      <c r="F196" t="b">
-        <v>0</v>
-      </c>
-      <c r="G196" t="inlineStr">
+      <c r="F196" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -6532,10 +5942,7 @@
           <t>Heater (Non-ISC)</t>
         </is>
       </c>
-      <c r="F197" t="b">
-        <v>0</v>
-      </c>
-      <c r="G197" t="inlineStr">
+      <c r="F197" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -6563,10 +5970,7 @@
           <t>Nail</t>
         </is>
       </c>
-      <c r="F198" t="b">
-        <v>0</v>
-      </c>
-      <c r="G198" t="inlineStr">
+      <c r="F198" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -6594,10 +5998,7 @@
           <t>Nail</t>
         </is>
       </c>
-      <c r="F199" t="b">
-        <v>0</v>
-      </c>
-      <c r="G199" t="inlineStr">
+      <c r="F199" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -6625,10 +6026,7 @@
           <t>Nail</t>
         </is>
       </c>
-      <c r="F200" t="b">
-        <v>0</v>
-      </c>
-      <c r="G200" t="inlineStr">
+      <c r="F200" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -6656,10 +6054,7 @@
           <t>Nail</t>
         </is>
       </c>
-      <c r="F201" t="b">
-        <v>0</v>
-      </c>
-      <c r="G201" t="inlineStr">
+      <c r="F201" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -6687,10 +6082,7 @@
           <t>Nail</t>
         </is>
       </c>
-      <c r="F202" t="b">
-        <v>0</v>
-      </c>
-      <c r="G202" t="inlineStr">
+      <c r="F202" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -6718,10 +6110,7 @@
           <t>Nail</t>
         </is>
       </c>
-      <c r="F203" t="b">
-        <v>0</v>
-      </c>
-      <c r="G203" t="inlineStr">
+      <c r="F203" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -6749,10 +6138,7 @@
           <t>Nail</t>
         </is>
       </c>
-      <c r="F204" t="b">
-        <v>0</v>
-      </c>
-      <c r="G204" t="inlineStr">
+      <c r="F204" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -6780,10 +6166,7 @@
           <t>Nail</t>
         </is>
       </c>
-      <c r="F205" t="b">
-        <v>0</v>
-      </c>
-      <c r="G205" t="inlineStr">
+      <c r="F205" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -6811,10 +6194,7 @@
           <t>Nail</t>
         </is>
       </c>
-      <c r="F206" t="b">
-        <v>0</v>
-      </c>
-      <c r="G206" t="inlineStr">
+      <c r="F206" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -6842,10 +6222,7 @@
           <t>Heater (Non-ISC)</t>
         </is>
       </c>
-      <c r="F207" t="b">
-        <v>0</v>
-      </c>
-      <c r="G207" t="inlineStr">
+      <c r="F207" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -6873,10 +6250,7 @@
           <t>Heater (Non-ISC)</t>
         </is>
       </c>
-      <c r="F208" t="b">
-        <v>0</v>
-      </c>
-      <c r="G208" t="inlineStr">
+      <c r="F208" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -6904,10 +6278,7 @@
           <t>Heater (Non-ISC)</t>
         </is>
       </c>
-      <c r="F209" t="b">
-        <v>0</v>
-      </c>
-      <c r="G209" t="inlineStr">
+      <c r="F209" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -6935,10 +6306,7 @@
           <t>Heater (Non-ISC)</t>
         </is>
       </c>
-      <c r="F210" t="b">
-        <v>0</v>
-      </c>
-      <c r="G210" t="inlineStr">
+      <c r="F210" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -6966,10 +6334,7 @@
           <t>Heater (Non-ISC)</t>
         </is>
       </c>
-      <c r="F211" t="b">
-        <v>0</v>
-      </c>
-      <c r="G211" t="inlineStr">
+      <c r="F211" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -6997,10 +6362,7 @@
           <t>Heater (Non-ISC)</t>
         </is>
       </c>
-      <c r="F212" t="b">
-        <v>0</v>
-      </c>
-      <c r="G212" t="inlineStr">
+      <c r="F212" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -7028,10 +6390,7 @@
           <t>Heater (Non-ISC)</t>
         </is>
       </c>
-      <c r="F213" t="b">
-        <v>0</v>
-      </c>
-      <c r="G213" t="inlineStr">
+      <c r="F213" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -7059,10 +6418,7 @@
           <t>Heater (Non-ISC)</t>
         </is>
       </c>
-      <c r="F214" t="b">
-        <v>0</v>
-      </c>
-      <c r="G214" t="inlineStr">
+      <c r="F214" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -7090,10 +6446,7 @@
           <t>Heater (Non-ISC)</t>
         </is>
       </c>
-      <c r="F215" t="b">
-        <v>0</v>
-      </c>
-      <c r="G215" t="inlineStr">
+      <c r="F215" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -7121,10 +6474,7 @@
           <t>Heater (Non-ISC)</t>
         </is>
       </c>
-      <c r="F216" t="b">
-        <v>0</v>
-      </c>
-      <c r="G216" t="inlineStr">
+      <c r="F216" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -7152,10 +6502,7 @@
           <t>Heater (Non-ISC)</t>
         </is>
       </c>
-      <c r="F217" t="b">
-        <v>0</v>
-      </c>
-      <c r="G217" t="inlineStr">
+      <c r="F217" t="inlineStr">
         <is>
           <t>High</t>
         </is>
@@ -7183,10 +6530,7 @@
           <t>Heater (Non-ISC)</t>
         </is>
       </c>
-      <c r="F218" t="b">
-        <v>1</v>
-      </c>
-      <c r="G218" t="inlineStr">
+      <c r="F218" t="inlineStr">
         <is>
           <t>High</t>
         </is>
@@ -7214,10 +6558,7 @@
           <t>Heater (Non-ISC)</t>
         </is>
       </c>
-      <c r="F219" t="b">
-        <v>0</v>
-      </c>
-      <c r="G219" t="inlineStr">
+      <c r="F219" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -7245,10 +6586,7 @@
           <t>Heater (Non-ISC)</t>
         </is>
       </c>
-      <c r="F220" t="b">
-        <v>0</v>
-      </c>
-      <c r="G220" t="inlineStr">
+      <c r="F220" t="inlineStr">
         <is>
           <t>High</t>
         </is>
@@ -7276,10 +6614,7 @@
           <t>Heater (Non-ISC)</t>
         </is>
       </c>
-      <c r="F221" t="b">
-        <v>0</v>
-      </c>
-      <c r="G221" t="inlineStr">
+      <c r="F221" t="inlineStr">
         <is>
           <t>High</t>
         </is>
@@ -7307,10 +6642,7 @@
           <t>Heater (Non-ISC)</t>
         </is>
       </c>
-      <c r="F222" t="b">
-        <v>0</v>
-      </c>
-      <c r="G222" t="inlineStr">
+      <c r="F222" t="inlineStr">
         <is>
           <t>High</t>
         </is>
@@ -7338,10 +6670,7 @@
           <t>Heater (Non-ISC)</t>
         </is>
       </c>
-      <c r="F223" t="b">
-        <v>0</v>
-      </c>
-      <c r="G223" t="inlineStr">
+      <c r="F223" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -7369,10 +6698,7 @@
           <t>Heater (Non-ISC)</t>
         </is>
       </c>
-      <c r="F224" t="b">
-        <v>0</v>
-      </c>
-      <c r="G224" t="inlineStr">
+      <c r="F224" t="inlineStr">
         <is>
           <t>High</t>
         </is>
@@ -7400,10 +6726,7 @@
           <t>Heater (Non-ISC)</t>
         </is>
       </c>
-      <c r="F225" t="b">
-        <v>0</v>
-      </c>
-      <c r="G225" t="inlineStr">
+      <c r="F225" t="inlineStr">
         <is>
           <t>High</t>
         </is>
@@ -7431,10 +6754,7 @@
           <t>Heater (Non-ISC)</t>
         </is>
       </c>
-      <c r="F226" t="b">
-        <v>0</v>
-      </c>
-      <c r="G226" t="inlineStr">
+      <c r="F226" t="inlineStr">
         <is>
           <t>High</t>
         </is>
@@ -7462,10 +6782,7 @@
           <t>Heater (Non-ISC)</t>
         </is>
       </c>
-      <c r="F227" t="b">
-        <v>0</v>
-      </c>
-      <c r="G227" t="inlineStr">
+      <c r="F227" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -7493,10 +6810,7 @@
           <t>Heater (Non-ISC)</t>
         </is>
       </c>
-      <c r="F228" t="b">
-        <v>0</v>
-      </c>
-      <c r="G228" t="inlineStr">
+      <c r="F228" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -7524,10 +6838,7 @@
           <t>Heater (Non-ISC)</t>
         </is>
       </c>
-      <c r="F229" t="b">
-        <v>0</v>
-      </c>
-      <c r="G229" t="inlineStr">
+      <c r="F229" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -7555,10 +6866,7 @@
           <t>Heater (Non-ISC)</t>
         </is>
       </c>
-      <c r="F230" t="b">
-        <v>0</v>
-      </c>
-      <c r="G230" t="inlineStr">
+      <c r="F230" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -7586,10 +6894,7 @@
           <t>Heater (Non-ISC)</t>
         </is>
       </c>
-      <c r="F231" t="b">
-        <v>0</v>
-      </c>
-      <c r="G231" t="inlineStr">
+      <c r="F231" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -7617,10 +6922,7 @@
           <t>Heater (Non-ISC)</t>
         </is>
       </c>
-      <c r="F232" t="b">
-        <v>0</v>
-      </c>
-      <c r="G232" t="inlineStr">
+      <c r="F232" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -7648,10 +6950,7 @@
           <t>Heater (Non-ISC)</t>
         </is>
       </c>
-      <c r="F233" t="b">
-        <v>0</v>
-      </c>
-      <c r="G233" t="inlineStr">
+      <c r="F233" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -7679,10 +6978,7 @@
           <t>Heater (Non-ISC)</t>
         </is>
       </c>
-      <c r="F234" t="b">
-        <v>0</v>
-      </c>
-      <c r="G234" t="inlineStr">
+      <c r="F234" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -7710,10 +7006,7 @@
           <t>Heater (Non-ISC)</t>
         </is>
       </c>
-      <c r="F235" t="b">
-        <v>0</v>
-      </c>
-      <c r="G235" t="inlineStr">
+      <c r="F235" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -7741,10 +7034,7 @@
           <t>Heater (Non-ISC)</t>
         </is>
       </c>
-      <c r="F236" t="b">
-        <v>0</v>
-      </c>
-      <c r="G236" t="inlineStr">
+      <c r="F236" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -7772,10 +7062,7 @@
           <t>Heater (Non-ISC)</t>
         </is>
       </c>
-      <c r="F237" t="b">
-        <v>0</v>
-      </c>
-      <c r="G237" t="inlineStr">
+      <c r="F237" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -7803,10 +7090,7 @@
           <t>Heater (Non-ISC)</t>
         </is>
       </c>
-      <c r="F238" t="b">
-        <v>0</v>
-      </c>
-      <c r="G238" t="inlineStr">
+      <c r="F238" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -7834,10 +7118,7 @@
           <t>Heater (Non-ISC)</t>
         </is>
       </c>
-      <c r="F239" t="b">
-        <v>1</v>
-      </c>
-      <c r="G239" t="inlineStr">
+      <c r="F239" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -7865,10 +7146,7 @@
           <t>Heater (Non-ISC)</t>
         </is>
       </c>
-      <c r="F240" t="b">
-        <v>0</v>
-      </c>
-      <c r="G240" t="inlineStr">
+      <c r="F240" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -7896,10 +7174,7 @@
           <t>Heater (Non-ISC)</t>
         </is>
       </c>
-      <c r="F241" t="b">
-        <v>0</v>
-      </c>
-      <c r="G241" t="inlineStr">
+      <c r="F241" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -7927,10 +7202,7 @@
           <t>Heater (Non-ISC)</t>
         </is>
       </c>
-      <c r="F242" t="b">
-        <v>0</v>
-      </c>
-      <c r="G242" t="inlineStr">
+      <c r="F242" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -7958,10 +7230,7 @@
           <t>Heater (Non-ISC)</t>
         </is>
       </c>
-      <c r="F243" t="b">
-        <v>1</v>
-      </c>
-      <c r="G243" t="inlineStr">
+      <c r="F243" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -7989,10 +7258,7 @@
           <t>Heater (Non-ISC)</t>
         </is>
       </c>
-      <c r="F244" t="b">
-        <v>0</v>
-      </c>
-      <c r="G244" t="inlineStr">
+      <c r="F244" t="inlineStr">
         <is>
           <t>High</t>
         </is>
@@ -8020,10 +7286,7 @@
           <t>Heater (Non-ISC)</t>
         </is>
       </c>
-      <c r="F245" t="b">
-        <v>1</v>
-      </c>
-      <c r="G245" t="inlineStr">
+      <c r="F245" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -8051,10 +7314,7 @@
           <t>Heater (Non-ISC)</t>
         </is>
       </c>
-      <c r="F246" t="b">
-        <v>0</v>
-      </c>
-      <c r="G246" t="inlineStr">
+      <c r="F246" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -8082,10 +7342,7 @@
           <t>Heater (Non-ISC)</t>
         </is>
       </c>
-      <c r="F247" t="b">
-        <v>1</v>
-      </c>
-      <c r="G247" t="inlineStr">
+      <c r="F247" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -8113,10 +7370,7 @@
           <t>Heater (Non-ISC)</t>
         </is>
       </c>
-      <c r="F248" t="b">
-        <v>0</v>
-      </c>
-      <c r="G248" t="inlineStr">
+      <c r="F248" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -8144,10 +7398,7 @@
           <t>Heater (Non-ISC)</t>
         </is>
       </c>
-      <c r="F249" t="b">
-        <v>1</v>
-      </c>
-      <c r="G249" t="inlineStr">
+      <c r="F249" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -8175,10 +7426,7 @@
           <t>Heater (Non-ISC)</t>
         </is>
       </c>
-      <c r="F250" t="b">
-        <v>0</v>
-      </c>
-      <c r="G250" t="inlineStr">
+      <c r="F250" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -8206,10 +7454,7 @@
           <t>Heater (Non-ISC)</t>
         </is>
       </c>
-      <c r="F251" t="b">
-        <v>0</v>
-      </c>
-      <c r="G251" t="inlineStr">
+      <c r="F251" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -8237,10 +7482,7 @@
           <t>Heater (Non-ISC)</t>
         </is>
       </c>
-      <c r="F252" t="b">
-        <v>0</v>
-      </c>
-      <c r="G252" t="inlineStr">
+      <c r="F252" t="inlineStr">
         <is>
           <t>High</t>
         </is>
@@ -8268,10 +7510,7 @@
           <t>Heater (Non-ISC)</t>
         </is>
       </c>
-      <c r="F253" t="b">
-        <v>0</v>
-      </c>
-      <c r="G253" t="inlineStr">
+      <c r="F253" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -8299,10 +7538,7 @@
           <t>Heater (Non-ISC)</t>
         </is>
       </c>
-      <c r="F254" t="b">
-        <v>0</v>
-      </c>
-      <c r="G254" t="inlineStr">
+      <c r="F254" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -8330,10 +7566,7 @@
           <t>Heater (ISC)</t>
         </is>
       </c>
-      <c r="F255" t="b">
-        <v>0</v>
-      </c>
-      <c r="G255" t="inlineStr">
+      <c r="F255" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -8361,10 +7594,7 @@
           <t>Heater (ISC)</t>
         </is>
       </c>
-      <c r="F256" t="b">
-        <v>0</v>
-      </c>
-      <c r="G256" t="inlineStr">
+      <c r="F256" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -8392,10 +7622,7 @@
           <t>Heater (ISC)</t>
         </is>
       </c>
-      <c r="F257" t="b">
-        <v>0</v>
-      </c>
-      <c r="G257" t="inlineStr">
+      <c r="F257" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -8423,10 +7650,7 @@
           <t>Heater (ISC)</t>
         </is>
       </c>
-      <c r="F258" t="b">
-        <v>0</v>
-      </c>
-      <c r="G258" t="inlineStr">
+      <c r="F258" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -8454,10 +7678,7 @@
           <t>Heater (ISC)</t>
         </is>
       </c>
-      <c r="F259" t="b">
-        <v>0</v>
-      </c>
-      <c r="G259" t="inlineStr">
+      <c r="F259" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -8485,10 +7706,7 @@
           <t>Heater (Non-ISC)</t>
         </is>
       </c>
-      <c r="F260" t="b">
-        <v>0</v>
-      </c>
-      <c r="G260" t="inlineStr">
+      <c r="F260" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -8516,10 +7734,7 @@
           <t>Heater (Non-ISC)</t>
         </is>
       </c>
-      <c r="F261" t="b">
-        <v>0</v>
-      </c>
-      <c r="G261" t="inlineStr">
+      <c r="F261" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -8547,10 +7762,7 @@
           <t>Heater (Non-ISC)</t>
         </is>
       </c>
-      <c r="F262" t="b">
-        <v>0</v>
-      </c>
-      <c r="G262" t="inlineStr">
+      <c r="F262" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -8578,10 +7790,7 @@
           <t>Nail</t>
         </is>
       </c>
-      <c r="F263" t="b">
-        <v>0</v>
-      </c>
-      <c r="G263" t="inlineStr">
+      <c r="F263" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -8609,10 +7818,7 @@
           <t>Heater (ISC)</t>
         </is>
       </c>
-      <c r="F264" t="b">
-        <v>0</v>
-      </c>
-      <c r="G264" t="inlineStr">
+      <c r="F264" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -8640,10 +7846,7 @@
           <t>Heater (ISC)</t>
         </is>
       </c>
-      <c r="F265" t="b">
-        <v>0</v>
-      </c>
-      <c r="G265" t="inlineStr">
+      <c r="F265" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -8671,10 +7874,7 @@
           <t>Heater (ISC)</t>
         </is>
       </c>
-      <c r="F266" t="b">
-        <v>0</v>
-      </c>
-      <c r="G266" t="inlineStr">
+      <c r="F266" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -8702,10 +7902,7 @@
           <t>Heater (Non-ISC)</t>
         </is>
       </c>
-      <c r="F267" t="b">
-        <v>0</v>
-      </c>
-      <c r="G267" t="inlineStr">
+      <c r="F267" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -8733,10 +7930,7 @@
           <t>Heater (Non-ISC)</t>
         </is>
       </c>
-      <c r="F268" t="b">
-        <v>0</v>
-      </c>
-      <c r="G268" t="inlineStr">
+      <c r="F268" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -8764,10 +7958,7 @@
           <t>Heater (Non-ISC)</t>
         </is>
       </c>
-      <c r="F269" t="b">
-        <v>0</v>
-      </c>
-      <c r="G269" t="inlineStr">
+      <c r="F269" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -8795,10 +7986,7 @@
           <t>Heater (ISC)</t>
         </is>
       </c>
-      <c r="F270" t="b">
-        <v>0</v>
-      </c>
-      <c r="G270" t="inlineStr">
+      <c r="F270" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -8826,10 +8014,7 @@
           <t>Heater (ISC)</t>
         </is>
       </c>
-      <c r="F271" t="b">
-        <v>0</v>
-      </c>
-      <c r="G271" t="inlineStr">
+      <c r="F271" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -8857,10 +8042,7 @@
           <t>Heater (ISC)</t>
         </is>
       </c>
-      <c r="F272" t="b">
-        <v>0</v>
-      </c>
-      <c r="G272" t="inlineStr">
+      <c r="F272" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -8888,10 +8070,7 @@
           <t>Heater (Non-ISC)</t>
         </is>
       </c>
-      <c r="F273" t="b">
-        <v>0</v>
-      </c>
-      <c r="G273" t="inlineStr">
+      <c r="F273" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -8919,10 +8098,7 @@
           <t>Heater (Non-ISC)</t>
         </is>
       </c>
-      <c r="F274" t="b">
-        <v>0</v>
-      </c>
-      <c r="G274" t="inlineStr">
+      <c r="F274" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -8950,10 +8126,7 @@
           <t>Heater (Non-ISC)</t>
         </is>
       </c>
-      <c r="F275" t="b">
-        <v>0</v>
-      </c>
-      <c r="G275" t="inlineStr">
+      <c r="F275" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -8981,10 +8154,7 @@
           <t>Nail</t>
         </is>
       </c>
-      <c r="F276" t="b">
-        <v>0</v>
-      </c>
-      <c r="G276" t="inlineStr">
+      <c r="F276" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -9012,10 +8182,7 @@
           <t>Nail</t>
         </is>
       </c>
-      <c r="F277" t="b">
-        <v>0</v>
-      </c>
-      <c r="G277" t="inlineStr">
+      <c r="F277" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -9043,10 +8210,7 @@
           <t>Nail</t>
         </is>
       </c>
-      <c r="F278" t="b">
-        <v>0</v>
-      </c>
-      <c r="G278" t="inlineStr">
+      <c r="F278" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -9074,10 +8238,7 @@
           <t>Heater (ISC)</t>
         </is>
       </c>
-      <c r="F279" t="b">
-        <v>0</v>
-      </c>
-      <c r="G279" t="inlineStr">
+      <c r="F279" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -9105,10 +8266,7 @@
           <t>Heater (ISC)</t>
         </is>
       </c>
-      <c r="F280" t="b">
-        <v>0</v>
-      </c>
-      <c r="G280" t="inlineStr">
+      <c r="F280" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -9136,10 +8294,7 @@
           <t>Heater (Non-ISC)</t>
         </is>
       </c>
-      <c r="F281" t="b">
-        <v>0</v>
-      </c>
-      <c r="G281" t="inlineStr">
+      <c r="F281" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -9167,10 +8322,7 @@
           <t>Heater (Non-ISC)</t>
         </is>
       </c>
-      <c r="F282" t="b">
-        <v>0</v>
-      </c>
-      <c r="G282" t="inlineStr">
+      <c r="F282" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -9198,10 +8350,7 @@
           <t>Nail</t>
         </is>
       </c>
-      <c r="F283" t="b">
-        <v>0</v>
-      </c>
-      <c r="G283" t="inlineStr">
+      <c r="F283" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -9229,10 +8378,7 @@
           <t>Heater (ISC)</t>
         </is>
       </c>
-      <c r="F284" t="b">
-        <v>0</v>
-      </c>
-      <c r="G284" t="inlineStr">
+      <c r="F284" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -9260,10 +8406,7 @@
           <t>Heater (ISC)</t>
         </is>
       </c>
-      <c r="F285" t="b">
-        <v>0</v>
-      </c>
-      <c r="G285" t="inlineStr">
+      <c r="F285" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -9291,10 +8434,7 @@
           <t>Heater (ISC)</t>
         </is>
       </c>
-      <c r="F286" t="b">
-        <v>0</v>
-      </c>
-      <c r="G286" t="inlineStr">
+      <c r="F286" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -9322,10 +8462,7 @@
           <t>Heater (ISC)</t>
         </is>
       </c>
-      <c r="F287" t="b">
-        <v>0</v>
-      </c>
-      <c r="G287" t="inlineStr">
+      <c r="F287" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -9353,10 +8490,7 @@
           <t>Heater (Non-ISC)</t>
         </is>
       </c>
-      <c r="F288" t="b">
-        <v>0</v>
-      </c>
-      <c r="G288" t="inlineStr">
+      <c r="F288" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -9384,10 +8518,7 @@
           <t>Heater (Non-ISC)</t>
         </is>
       </c>
-      <c r="F289" t="b">
-        <v>0</v>
-      </c>
-      <c r="G289" t="inlineStr">
+      <c r="F289" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -9415,10 +8546,7 @@
           <t>Heater (Non-ISC)</t>
         </is>
       </c>
-      <c r="F290" t="b">
-        <v>0</v>
-      </c>
-      <c r="G290" t="inlineStr">
+      <c r="F290" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -9446,10 +8574,7 @@
           <t>Heater (Non-ISC)</t>
         </is>
       </c>
-      <c r="F291" t="b">
-        <v>0</v>
-      </c>
-      <c r="G291" t="inlineStr">
+      <c r="F291" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -9477,10 +8602,7 @@
           <t>Heater (Non-ISC)</t>
         </is>
       </c>
-      <c r="F292" t="b">
-        <v>0</v>
-      </c>
-      <c r="G292" t="inlineStr">
+      <c r="F292" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -9508,10 +8630,7 @@
           <t>Heater (Non-ISC)</t>
         </is>
       </c>
-      <c r="F293" t="b">
-        <v>0</v>
-      </c>
-      <c r="G293" t="inlineStr">
+      <c r="F293" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -9539,10 +8658,7 @@
           <t>Nail</t>
         </is>
       </c>
-      <c r="F294" t="b">
-        <v>0</v>
-      </c>
-      <c r="G294" t="inlineStr">
+      <c r="F294" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -9570,10 +8686,7 @@
           <t>Nail</t>
         </is>
       </c>
-      <c r="F295" t="b">
-        <v>0</v>
-      </c>
-      <c r="G295" t="inlineStr">
+      <c r="F295" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -9601,10 +8714,7 @@
           <t>Heater (ISC)</t>
         </is>
       </c>
-      <c r="F296" t="b">
-        <v>0</v>
-      </c>
-      <c r="G296" t="inlineStr">
+      <c r="F296" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -9632,10 +8742,7 @@
           <t>Heater (ISC)</t>
         </is>
       </c>
-      <c r="F297" t="b">
-        <v>0</v>
-      </c>
-      <c r="G297" t="inlineStr">
+      <c r="F297" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -9663,10 +8770,7 @@
           <t>Heater (ISC)</t>
         </is>
       </c>
-      <c r="F298" t="b">
-        <v>0</v>
-      </c>
-      <c r="G298" t="inlineStr">
+      <c r="F298" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -9694,10 +8798,7 @@
           <t>Heater (ISC)</t>
         </is>
       </c>
-      <c r="F299" t="b">
-        <v>0</v>
-      </c>
-      <c r="G299" t="inlineStr">
+      <c r="F299" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -9725,10 +8826,7 @@
           <t>Heater (Non-ISC)</t>
         </is>
       </c>
-      <c r="F300" t="b">
-        <v>0</v>
-      </c>
-      <c r="G300" t="inlineStr">
+      <c r="F300" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -9756,10 +8854,7 @@
           <t>Heater (Non-ISC)</t>
         </is>
       </c>
-      <c r="F301" t="b">
-        <v>0</v>
-      </c>
-      <c r="G301" t="inlineStr">
+      <c r="F301" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -9787,10 +8882,7 @@
           <t>Heater (Non-ISC)</t>
         </is>
       </c>
-      <c r="F302" t="b">
-        <v>0</v>
-      </c>
-      <c r="G302" t="inlineStr">
+      <c r="F302" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -9818,10 +8910,7 @@
           <t>Heater (Non-ISC)</t>
         </is>
       </c>
-      <c r="F303" t="b">
-        <v>0</v>
-      </c>
-      <c r="G303" t="inlineStr">
+      <c r="F303" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -9849,10 +8938,7 @@
           <t>Nail</t>
         </is>
       </c>
-      <c r="F304" t="b">
-        <v>0</v>
-      </c>
-      <c r="G304" t="inlineStr">
+      <c r="F304" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -9880,10 +8966,7 @@
           <t>Nail</t>
         </is>
       </c>
-      <c r="F305" t="b">
-        <v>0</v>
-      </c>
-      <c r="G305" t="inlineStr">
+      <c r="F305" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -9911,10 +8994,7 @@
           <t>Nail</t>
         </is>
       </c>
-      <c r="F306" t="b">
-        <v>0</v>
-      </c>
-      <c r="G306" t="inlineStr">
+      <c r="F306" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -9942,10 +9022,7 @@
           <t>Heater (ISC)</t>
         </is>
       </c>
-      <c r="F307" t="b">
-        <v>0</v>
-      </c>
-      <c r="G307" t="inlineStr">
+      <c r="F307" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -9973,10 +9050,7 @@
           <t>Heater (ISC)</t>
         </is>
       </c>
-      <c r="F308" t="b">
-        <v>0</v>
-      </c>
-      <c r="G308" t="inlineStr">
+      <c r="F308" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -10004,10 +9078,7 @@
           <t>Heater (ISC)</t>
         </is>
       </c>
-      <c r="F309" t="b">
-        <v>0</v>
-      </c>
-      <c r="G309" t="inlineStr">
+      <c r="F309" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -10035,10 +9106,7 @@
           <t>Heater (ISC)</t>
         </is>
       </c>
-      <c r="F310" t="b">
-        <v>0</v>
-      </c>
-      <c r="G310" t="inlineStr">
+      <c r="F310" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -10066,10 +9134,7 @@
           <t>Heater (Non-ISC)</t>
         </is>
       </c>
-      <c r="F311" t="b">
-        <v>0</v>
-      </c>
-      <c r="G311" t="inlineStr">
+      <c r="F311" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -10097,10 +9162,7 @@
           <t>Heater (Non-ISC)</t>
         </is>
       </c>
-      <c r="F312" t="b">
-        <v>0</v>
-      </c>
-      <c r="G312" t="inlineStr">
+      <c r="F312" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -10128,10 +9190,7 @@
           <t>Nail</t>
         </is>
       </c>
-      <c r="F313" t="b">
-        <v>0</v>
-      </c>
-      <c r="G313" t="inlineStr">
+      <c r="F313" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -10159,10 +9218,7 @@
           <t>Nail</t>
         </is>
       </c>
-      <c r="F314" t="b">
-        <v>0</v>
-      </c>
-      <c r="G314" t="inlineStr">
+      <c r="F314" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -10190,10 +9246,7 @@
           <t>Nail</t>
         </is>
       </c>
-      <c r="F315" t="b">
-        <v>0</v>
-      </c>
-      <c r="G315" t="inlineStr">
+      <c r="F315" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
